--- a/data/trans_orig/IP3108-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP3108-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>531</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>519</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39368</t>
+          <t>38721</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45606</t>
+          <t>45269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43135</t>
+          <t>42426</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85567</t>
+          <t>85813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94637</t>
+          <t>94203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>14580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72725</t>
+          <t>72944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83499</t>
+          <t>83598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88506</t>
+          <t>88292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97734</t>
+          <t>97707</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>165024</t>
+          <t>165574</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179831</t>
+          <t>179585</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55447</t>
+          <t>54786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61213</t>
+          <t>61238</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61403</t>
+          <t>61500</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>119466</t>
+          <t>119129</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126480</t>
+          <t>126489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>525</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61357</t>
+          <t>60426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68198</t>
+          <t>67827</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62121</t>
+          <t>62390</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71278</t>
+          <t>71274</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>125928</t>
+          <t>126010</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>137329</t>
+          <t>137638</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31296</t>
+          <t>30861</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>37357</t>
+          <t>37375</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>31702</t>
+          <t>32170</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>39255</t>
+          <t>39274</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65698</t>
+          <t>66005</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>75630</t>
+          <t>75312</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>46463</t>
+          <t>45912</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>52130</t>
+          <t>52037</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>50940</t>
+          <t>50821</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>56556</t>
+          <t>56539</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>99473</t>
+          <t>99672</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>107880</t>
+          <t>107797</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8246</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>104949</t>
+          <t>105561</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>115473</t>
+          <t>115559</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>107454</t>
+          <t>106950</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>117717</t>
+          <t>117165</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>216204</t>
+          <t>214972</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>231647</t>
+          <t>230629</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11405</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>15851</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>123080</t>
+          <t>122678</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>134119</t>
+          <t>133973</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>133130</t>
+          <t>132815</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>143581</t>
+          <t>143304</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>260204</t>
+          <t>258685</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>275180</t>
+          <t>275173</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>30165</t>
+          <t>29774</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>29325</t>
+          <t>29576</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>30062</t>
+          <t>30279</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>31347</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>56926</t>
+          <t>56302</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>10674</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>23544</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>35064</t>
+          <t>35507</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>559438</t>
+          <t>559304</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>582590</t>
+          <t>583117</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>603004</t>
+          <t>605200</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>626989</t>
+          <t>627636</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1171440</t>
+          <t>1170816</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1204376</t>
+          <t>1205037</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>498</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>9276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>708</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>842</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35995</t>
+          <t>35600</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45701</t>
+          <t>45675</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55424</t>
+          <t>55055</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60012</t>
+          <t>60013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92919</t>
+          <t>92729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105164</t>
+          <t>105099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,82 +7803,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4894</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>3847</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7865</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1821</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4846</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>3847</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>7754</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8069,42 +8069,42 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>3650</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>8403</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>4,43%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>3650</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>1355</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>8325</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83684</t>
+          <t>83452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91315</t>
+          <t>91364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>86240</t>
+          <t>85660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92713</t>
+          <t>92745</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171610</t>
+          <t>171677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182764</t>
+          <t>182649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54231</t>
+          <t>54625</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61119</t>
+          <t>61224</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59178</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63718</t>
+          <t>64356</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116778</t>
+          <t>116659</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124298</t>
+          <t>124090</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9157,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -9604,12 +9604,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>64202</t>
+          <t>64300</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70967</t>
+          <t>70961</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70894</t>
+          <t>71036</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>77687</t>
+          <t>77568</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>138029</t>
+          <t>137534</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>147843</t>
+          <t>146961</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -10173,12 +10173,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10188,12 +10188,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -10286,12 +10286,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33399</t>
+          <t>33391</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>40449</t>
+          <t>40267</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10301,12 +10301,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>35521</t>
+          <t>35830</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42451</t>
+          <t>42771</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>71434</t>
+          <t>71945</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>81526</t>
+          <t>81594</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -10968,12 +10968,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>40107</t>
+          <t>39885</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>47540</t>
+          <t>47568</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>44405</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>51101</t>
+          <t>50734</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11018,12 +11018,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>87953</t>
+          <t>87057</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>96890</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -11203,7 +11203,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>702</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>12385</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -11537,12 +11537,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -11650,12 +11650,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>106705</t>
+          <t>106916</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>116233</t>
+          <t>116372</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>116306</t>
+          <t>116770</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>125427</t>
+          <t>125442</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>228144</t>
+          <t>227827</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>240615</t>
+          <t>240138</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11735,12 +11735,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>610</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>13744</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -12219,12 +12219,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>11654</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>14284</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>9747</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>22478</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -12332,12 +12332,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>128835</t>
+          <t>129413</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>141936</t>
+          <t>141661</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>134377</t>
+          <t>135446</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>147502</t>
+          <t>147827</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>267696</t>
+          <t>269068</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>285823</t>
+          <t>286498</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>30544</t>
+          <t>31621</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>17839</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>28881</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>24453</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>42022</t>
+          <t>41717</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>24521</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>43976</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>574966</t>
+          <t>574626</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>599087</t>
+          <t>598841</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>626745</t>
+          <t>625489</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>648759</t>
+          <t>648376</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1209548</t>
+          <t>1209752</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1241066</t>
+          <t>1241410</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -13932,12 +13932,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44098</t>
+          <t>43499</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51203</t>
+          <t>51160</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13967,12 +13967,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49203</t>
+          <t>48835</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57748</t>
+          <t>57742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14002,12 +14002,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95572</t>
+          <t>95852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106658</t>
+          <t>107346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14017,12 +14017,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14350,7 +14350,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -14501,12 +14501,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>10971</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14516,12 +14516,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14536,12 +14536,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14551,12 +14551,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>17719</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14586,12 +14586,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -14614,12 +14614,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79052</t>
+          <t>79912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89073</t>
+          <t>89670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14649,12 +14649,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87389</t>
+          <t>87472</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97982</t>
+          <t>97744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14684,12 +14684,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171474</t>
+          <t>171234</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185158</t>
+          <t>184897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -14962,7 +14962,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -15188,7 +15188,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15223,7 +15223,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -15296,12 +15296,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50731</t>
+          <t>50867</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56583</t>
+          <t>56572</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15311,12 +15311,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60359</t>
+          <t>60373</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113712</t>
+          <t>114566</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -15381,12 +15381,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>857</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -15978,12 +15978,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>61794</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>69534</t>
+          <t>69554</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15993,12 +15993,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>69823</t>
+          <t>69510</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75464</t>
+          <t>75467</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16028,12 +16028,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>134170</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>143587</t>
+          <t>143966</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16063,12 +16063,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16632,12 +16632,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>35706</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -16695,12 +16695,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34399</t>
+          <t>34464</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>39495</t>
+          <t>39489</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16710,12 +16710,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>72722</t>
+          <t>72540</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>80364</t>
+          <t>80126</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16745,12 +16745,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16930,7 +16930,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16945,7 +16945,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>730</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17093,7 +17093,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17299,12 +17299,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -17342,12 +17342,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>40276</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>47842</t>
+          <t>47829</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17377,12 +17377,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>45512</t>
+          <t>45276</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>51845</t>
+          <t>51854</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>88387</t>
+          <t>88579</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>98188</t>
+          <t>98551</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17427,12 +17427,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17690,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17740,7 +17740,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17775,7 +17775,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>16872</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -17911,12 +17911,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17926,12 +17926,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17946,12 +17946,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>19195</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17961,12 +17961,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17981,12 +17981,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>11265</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>25126</t>
+          <t>25480</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17996,12 +17996,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>100642</t>
+          <t>100821</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>111663</t>
+          <t>111817</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18039,12 +18039,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18059,12 +18059,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>102407</t>
+          <t>102173</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>116244</t>
+          <t>115556</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -18074,12 +18074,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -18094,12 +18094,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>208319</t>
+          <t>207250</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>225663</t>
+          <t>224792</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18109,12 +18109,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18500,7 +18500,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -18593,12 +18593,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18608,12 +18608,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18628,12 +18628,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18643,12 +18643,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18663,12 +18663,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>21453</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18678,12 +18678,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -18706,12 +18706,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>130597</t>
+          <t>131471</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>141514</t>
+          <t>141675</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>140256</t>
+          <t>140126</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>149549</t>
+          <t>149585</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18756,12 +18756,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18776,12 +18776,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>275176</t>
+          <t>275872</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>289477</t>
+          <t>289427</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18791,12 +18791,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>18890</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19139,7 +19139,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>23939</t>
+          <t>23417</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>22460</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>40098</t>
+          <t>39584</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>34231</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>39425</t>
+          <t>39809</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>43914</t>
+          <t>43572</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>69069</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>571879</t>
+          <t>572041</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>594843</t>
+          <t>595494</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19403,12 +19403,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>615182</t>
+          <t>614476</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>638261</t>
+          <t>638464</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19438,12 +19438,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1196092</t>
+          <t>1194613</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1228129</t>
+          <t>1227350</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
